--- a/leads/Master_Leads_-_Cleanest_600.xlsx
+++ b/leads/Master_Leads_-_Cleanest_600.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H601"/>
+  <dimension ref="A1:G601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -466,11 +466,6 @@
           <t>Website</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -506,11 +501,6 @@
           <t>https://mamajoy.qa/</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Building 50, Street 210, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -546,11 +536,6 @@
           <t>https://signature.pooriandkarak.qa/</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Lusail - Marina, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -586,11 +571,6 @@
           <t>https://mogobogo.qa/</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Tornado Dune Plaza, Tornado Tower, 1st Floor, Majlis Al Taawon St, D</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -626,11 +606,6 @@
           <t>https://www.gocrispy.com/</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -666,11 +641,6 @@
           <t>https://almalqa.com/</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>الحي الثقافي - كتار, Shakespeare St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -706,11 +676,6 @@
           <t>https://marmarayistanbulrestaurant.com/</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Al Mansoura St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -746,11 +711,6 @@
           <t>http://www.sabahwmasa.com/</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Al Corniche, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -786,11 +746,6 @@
           <t>https://socialhouseqa.com/</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Lusail Marina Tower, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -826,11 +781,6 @@
           <t>https://kusinadoha.qa/</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Al Kinana St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -866,11 +816,6 @@
           <t>https://ninjaramen.qa/</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>5CXM+9V6, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -906,11 +851,6 @@
           <t>https://sushiponto.com/</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>The Pearl, Unit 110, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -946,11 +886,6 @@
           <t>https://www.thechippy.qa/</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Tornado Tower, Majlis Al Taawon St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -986,11 +921,6 @@
           <t>https://desidhaba.qa/</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Gate No 03, Second Floor, Tawar Mall, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1026,11 +956,6 @@
           <t>https://hundredcoffee.qa/</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Gewan Island, Crystal 5, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1066,11 +991,6 @@
           <t>http://www.basilcafe.qa/</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>8FJW+VR, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1106,11 +1026,6 @@
           <t>https://societe.com.qa/</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Zone 31 street 905 blg 16, Al Markhiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1146,11 +1061,6 @@
           <t>https://chocolatebash.qa/</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Place Vendôme Mall Gate 5, St. Germain Area, Floor 2, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1186,11 +1096,6 @@
           <t>https://greydoha.qa/</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Mesaieed Rd, Al Wakrah 5J54+H9M Al Wakrah, Mesaieed Rd, Al Wakrah</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1226,11 +1131,6 @@
           <t>https://www.littlesailor.com.qa/</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Street 213, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1266,11 +1166,6 @@
           <t>http://o2cafe.qa/</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Al Henaizbiah St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1306,11 +1201,6 @@
           <t>https://www.teatime.qa/</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>9GRG+M4H, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1346,11 +1236,6 @@
           <t>https://coffeistacatering.qa/</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Golf Club, Zone No: 52, Education City, Al Rayyan Road, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1386,11 +1271,6 @@
           <t>http://www.theloft.qa/</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Water Taxi 6, Porto Arabia Boardwalk, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1426,11 +1306,6 @@
           <t>https://twentyeight.qa/</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Shop 02 Building 60, Street 989, Zone 53 Al Shafi St, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1466,11 +1341,6 @@
           <t>https://www.zawyacoffee.qa/</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Mina District, Old, Building 34A, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1506,11 +1376,6 @@
           <t>http://1951cafe.com/</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Al Reem / Tatweer Tower, Conference Centre, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1546,11 +1411,6 @@
           <t>http://cherrybeans.com/</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Environment Street، الدوحة، ام لخبا منطقة رقم 31 شارع البيئةرقم 950</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1586,11 +1446,6 @@
           <t>https://www.casadr.org/</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Zone 33 879 Street Building No. 6, Markhiya, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1626,11 +1481,6 @@
           <t>https://www.maiachocolates.com/</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Lusail Commercial Boulevard, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1666,11 +1516,6 @@
           <t>http://www.pizzeriamargherita.com/en</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Al Mirqab Al Jadeed St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1706,11 +1551,6 @@
           <t>http://www.nooracafe.com/</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>6GF4+VRP, Industrial Area Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1746,11 +1586,6 @@
           <t>http://www.stormicafe.com/</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Centro, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1786,11 +1621,6 @@
           <t>http://www.lapcoffee.com/</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Stadium Entrance, 1 Al Waab St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1826,11 +1656,6 @@
           <t>https://www.dietcafe.com.qa/</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Al Waab St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1866,11 +1691,6 @@
           <t>https://frame.coffee/</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>55 Othman Bin Affan St, Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1906,11 +1726,6 @@
           <t>https://www.caffeconcerto.co.uk/locations/qatar</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1946,11 +1761,6 @@
           <t>https://www.swissotelcornichedoha.com/restaurants/chezelle/</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Corniche Park Towers, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1986,11 +1796,6 @@
           <t>http://www.delordcafe.com/</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Mina District, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2026,11 +1831,6 @@
           <t>https://www.dietcenter-qa.com/</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Street 445, Building No. 40 , Al Kharaitiyat , Umm Salal, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2066,11 +1866,6 @@
           <t>https://www.ergonfoods.com/ergon-qatar</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Al Abraj Park, Fasht Al Hool</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2106,11 +1901,6 @@
           <t>http://www.tigercookies.com.qa/</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>al jazeera petrol station, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2146,11 +1936,6 @@
           <t>http://www.qinwandates.com/</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>63, Maysaloun St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2186,11 +1971,6 @@
           <t>https://www.teasocialcafe-qa.com/</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Building -8, Street 880, Zone 22, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2226,11 +2006,6 @@
           <t>https://www.hamad.qa/EN/Hospitals-and-services/Hamad-Dental-Services/Pages/default.aspx</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Building 70 Street 810, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2266,11 +2041,6 @@
           <t>https://petvetcare.qa/</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Unit No. 9, Ras Abou Aboud, Building No. 48 Area 27 St. 210, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2306,11 +2076,6 @@
           <t>http://www.amannursing.com/</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>90 Ahmed Bin Mohammed Bin Thani St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2346,11 +2111,6 @@
           <t>https://www.alhadimedical.com/</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Al Luqta St, الريان</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2386,11 +2146,6 @@
           <t>https://alsalammedical-qa.com/</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Al Salam St, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2426,11 +2181,6 @@
           <t>http://www.alkhanjimedical.com/</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>4th Floor, Office No 407, Plaza Building, B Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2466,11 +2216,6 @@
           <t>https://en.alkharashy.com/</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>7F9F+7FX, Al Waab St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2506,11 +2251,6 @@
           <t>https://bostonmedcare.com/</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Building number 83,zone, 8FR9+G27, 31 Street 857، Doha</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2546,11 +2286,6 @@
           <t>https://kingsdentalcenter.com/</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Al mawrid street, Zone 64, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2586,11 +2321,6 @@
           <t>https://lcc.qa/en/</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>530 Al Kharaitiyat, Umm Salal Muhammed</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2626,11 +2356,6 @@
           <t>https://docmedc.com/</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>9GMF+QX4, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2666,11 +2391,6 @@
           <t>https://recoverylabqatar.com/</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Metro Station, Near Al Waab St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2706,11 +2426,6 @@
           <t>https://zaindentalcenter.com/</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bldg 28, Zone, 65 Al Bayan St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2746,11 +2461,6 @@
           <t>http://www.sultanpremier.com/</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Building No: 7, Street 445, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2786,11 +2496,6 @@
           <t>https://britemedicalcentre.com/</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Old airport, Jaber Bin Hayyan St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2826,11 +2531,6 @@
           <t>http://www.drkuttysmedicalcentre.com/</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Building #128, 2nd Floor, Street # 340, Midmac Roundabout, Near Salw</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2866,11 +2566,6 @@
           <t>http://hamc.qa/</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2906,11 +2601,6 @@
           <t>http://icbodycare.com/</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Mirqab Mall 2nd Floor, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2946,11 +2636,6 @@
           <t>http://www.royamedicalservices.com/</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Building No.108, 2nd Floor, Beside Al Shefa Polyclinic, D Ring Rd, D</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2986,11 +2671,6 @@
           <t>https://www.aioniswellness.com/</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Excellence Tower, Floor 22, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3026,11 +2706,6 @@
           <t>https://aqsamc.qa/</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>55 Al Waab St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3066,11 +2741,6 @@
           <t>https://www.ahcunani.com/sexologist-in-doha-qatar</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>No:13, street no 860 Al mahar street zone no 6 Old Ghanim road (behi</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3106,11 +2776,6 @@
           <t>http://avenuesdental.com/</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Mesaimeer Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3146,11 +2811,6 @@
           <t>https://doctoreyeoptics.com/</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>OPPOSITE FAMILY FOOD CENTER, Al Mirqab Al Jadeed St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3186,11 +2846,6 @@
           <t>https://medvedpodo.com/</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Street 319 Marina, Twin Towers - TOWER, Parking slots are always ava</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3226,11 +2881,6 @@
           <t>https://reliefmedical.qa/</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Laffan Tower, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3266,11 +2916,6 @@
           <t>https://www.sidra.org/</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3306,11 +2951,6 @@
           <t>http://www.skinmasters.qa/</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>313, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3346,11 +2986,6 @@
           <t>https://www.onfleekqatar.com/</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>213 Zone 66 Unit 20, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3386,11 +3021,6 @@
           <t>https://www.skinandsoulqa.com/</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Located in Staybridge suites doha Ground floor, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3426,11 +3056,6 @@
           <t>http://dohabeautycenter.com/</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Lulu Abu Sidra Mall, First Floor</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3466,11 +3091,6 @@
           <t>https://www.rosabellabc.com/</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bld 118 shop 2, zone 55, 180 Othman Bin Affan St, الريان</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3506,11 +3126,6 @@
           <t>https://www.equilibrium.qa/</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Zone 69 Building 108 Shops 13,14, 15 Street 303, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3546,11 +3161,6 @@
           <t>https://www.evolvemindbodysoul.com/</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Office 1, 2nd Floor, Al Fardan Center, Banks Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3586,11 +3196,6 @@
           <t>https://www.fyrefitdoha.com/</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>230 C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3626,11 +3231,6 @@
           <t>https://www.365zkfitnessclub.com/</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Al Mansoora, 42 Ibn Dirhem, Street 950, Zone 25, Building 43, Floor</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3666,11 +3266,6 @@
           <t>https://www.grandgoldgym.com/</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Al Mana Plaza Building Al Sadd 5th Floor Office 7, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3706,11 +3301,6 @@
           <t>https://www.alramiisc.qa/</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bu Samra، Street , 1706, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3746,11 +3336,6 @@
           <t>https://f45training.qa/westbay</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>8GCG+V2V, Maysaloun Street, Onaiza 63 2nd floor Wyndham Doha, Maysal</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3786,11 +3371,6 @@
           <t>http://www.fitzone.qa/</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>7F2P+F58, Haloul, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3826,11 +3406,6 @@
           <t>https://www.lapelota.qa/</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Al Andalus School Complex, Gate 5, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3866,11 +3441,6 @@
           <t>https://www.metimeqatar.com/</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Qatar sports club, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3906,11 +3476,6 @@
           <t>http://www.newidentity.qa/</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Building West Walk Area, Street 340, 316 Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3946,11 +3511,6 @@
           <t>http://www.orxsports.qa/</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Office 103 Center Building, 53 Street 840, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3986,11 +3546,6 @@
           <t>https://psgacademy.qa/</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Majlis Al Taawon St, Al Asmakh Tower, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4026,11 +3581,6 @@
           <t>https://shotokansportcenter.qa/</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Gharrafat Al Rayyan St, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4066,11 +3616,6 @@
           <t>http://www.20mfit.com/</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Laffan Tower, Laffan tower floor, الطابق 22 الدوحه, 22 Ambassadors S</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4106,11 +3651,6 @@
           <t>https://ascqa.com/</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>plaza Souq, 0000 Al Mamora, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4146,11 +3686,6 @@
           <t>https://www.blastersqatar.com/</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4186,11 +3721,6 @@
           <t>https://www.clementsports.com/</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>College, Al Wajba Campus, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4226,11 +3756,6 @@
           <t>http://www.globalgymdoha.com/</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Hazm Al Markhiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4266,11 +3791,6 @@
           <t>https://gulfsportsclub.com/</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>7FPW+F99, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4306,11 +3826,6 @@
           <t>https://iconfbacademy.com/</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Doha British School, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4346,11 +3861,6 @@
           <t>https://www.ninjavigor.com/</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>First Floor, Abu Hamour Dar Al Salam Mall, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4386,11 +3896,6 @@
           <t>http://www.spartasa.com/</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Al Jazeera St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4426,11 +3931,6 @@
           <t>https://squad5training.com/</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Excellence Tower, Unit 904, Al Shatt St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4466,11 +3966,6 @@
           <t>http://www.strongboxqatar.com/</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Doha Sports Park, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4506,11 +4001,6 @@
           <t>http://www.thebackyarddoha.com/</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>DOHA SPORTS PARK, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4546,11 +4036,6 @@
           <t>http://www.xfactorqa.com/</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>in AlMuftah، Plaza Building، Bin Mahmoud, Al Rayyan Road, Al Reem St</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4586,11 +4071,6 @@
           <t>http://www.esqalar.qa/</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Aspire zone Doha Qatar</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4626,11 +4106,6 @@
           <t>https://f45training.com/qa/studio/alsadd/</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Ahmed Bin Taimiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4666,11 +4141,6 @@
           <t>https://fs8.com/westbay/home</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>2nd Floor, Wyndham Doha, Maysaloun St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4706,11 +4176,6 @@
           <t>https://www.fortitude.qa/</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Dareen Tower, Al, Al Sham St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4746,11 +4211,6 @@
           <t>http://www.athletes-fit.com/</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Qatar Sports Club, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4786,11 +4246,6 @@
           <t>http://www.livelifeqatar.com/</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Intercontinental Doha, Al Istiqlal Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4826,11 +4281,6 @@
           <t>https://www.qatarkarate.com/</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Near Lulu Hypermarket, Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -4866,11 +4316,6 @@
           <t>https://www.asasportsqatar.com/</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>ابو هامور, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4906,11 +4351,6 @@
           <t>https://www.bpt.com.qa/</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Al-Mirqab Mall, Block-J Second Floor 205, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4946,11 +4386,6 @@
           <t>https://cityfitnessgym.fitness/</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>1ST Floor, 7GGQ+26 Near to crazy signal, B Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4986,11 +4421,6 @@
           <t>https://mastersmartialartsintl.com/</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Floor 1, Bldg. No 270, Street 230, Al Mansoura St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5026,11 +4456,6 @@
           <t>https://qbhoops.com/</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Al Nebras International School, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5066,11 +4491,6 @@
           <t>https://theindoorster.com/</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Tornado Tower Level 27, Majlis Al Taawon St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5106,11 +4526,6 @@
           <t>https://sportsvision.club/</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Al Tarfa Lusail, Wadi Al Banat, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5146,11 +4561,6 @@
           <t>http://www.alwadan.qa/</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>342 Aljazera st 342 Aljazera st, Ibn Mahmoud</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5186,11 +4596,6 @@
           <t>https://halawkakaw.com/</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>160, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5226,11 +4631,6 @@
           <t>https://www.regencyhypermarket.com/</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>8CPV+3WP, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5266,11 +4666,6 @@
           <t>https://www.monoprix.qa/branch_list/tower-13-porto-arabia/</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>3, 63, Lagune</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5306,11 +4701,6 @@
           <t>https://almalakifresh.com/</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>8F6Q+84V Bldg No:294 Street No:244, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5346,11 +4736,6 @@
           <t>http://www.adconqatar.com/</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sterrt 47, Zone 57 , Building No, 532 Street 45, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5386,11 +4771,6 @@
           <t>https://qatarfurnituremarket.com/</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>797</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5426,11 +4806,6 @@
           <t>https://selectionfurnitureqa.com/</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5466,11 +4841,6 @@
           <t>https://fineartqatar.com/product-category/symbol-mattress/</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>E Industrial St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5506,11 +4876,6 @@
           <t>https://bughunaimauto.com/</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>zone 52, building number 363, shop number, 6 Street 990, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -5546,11 +4911,6 @@
           <t>http://volexqa.com/</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>17 Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5586,11 +4946,6 @@
           <t>https://qatarfurniture.qa/</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Souq Al Haraj, Shop No:13, Street 850, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5626,11 +4981,6 @@
           <t>https://alruhulfurniture.com/</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Al Mansoura St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5666,11 +5016,6 @@
           <t>https://goodchoicefurnituredoha.com/</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Umm Al Doom, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5706,11 +5051,6 @@
           <t>http://www.onlineshopping.qa/</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>815 Al Safliya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5746,11 +5086,6 @@
           <t>http://www.dohansqatar.com/</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>1st Floor Office, Street 205, 19 Salwa Rd</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5786,11 +5121,6 @@
           <t>https://www.hempel.com/en-me</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Building 226 Street 280, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5826,11 +5156,6 @@
           <t>http://www.executeinteriors.com/</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Face to gulf cinema, signal</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -5866,11 +5191,6 @@
           <t>https://maspaints.com/</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Najma St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5906,11 +5226,6 @@
           <t>http://www.ndcqatar.com/</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Majlis Al Taawon St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5946,11 +5261,6 @@
           <t>https://partyballoondohaqatar.com/</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5986,11 +5296,6 @@
           <t>http://wowzerqatar.com/</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Transworld tower, Office 4, Fifth Floor, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6096,11 +5401,6 @@
           <t>https://circuitstore.qa/</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6136,11 +5436,6 @@
           <t>https://alothmanfashion.com/</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Barahat Msheireb St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6176,11 +5471,6 @@
           <t>https://artlandinterior-qa.com/</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bin Al Sheikh, Grand Hammad Street، Doha</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6216,11 +5506,6 @@
           <t>https://www.pfdesigncenter-qatar.com/</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Building 36, Zone, 3 الوادي، Doha</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6256,11 +5541,6 @@
           <t>https://savingsquareonline.com/</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Ahmed Bin Ali, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6296,11 +5576,6 @@
           <t>https://alabadelafurniture.com/</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6336,11 +5611,6 @@
           <t>https://www.aspireblindsdoha.com/</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Gate No:, 136 Street No: 3083, Birkat Al Awamer</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6376,11 +5646,6 @@
           <t>https://bankokcurtainstore.com/</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Souq Al Haraj, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6416,11 +5681,6 @@
           <t>https://qatarglassmainten.com/</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Souk Al Haraj, 850 Al Mansoura St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6456,11 +5716,6 @@
           <t>https://uniqueinteriordesigndoha.com/</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Najma Post Box No: 22911, 980 Ibn Firnas St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6566,11 +5821,6 @@
           <t>http://althurayakg.com/</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>7G5V+Q45, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6606,11 +5856,6 @@
           <t>http://www.acsqatar.net/</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>St 300, Al Wukair</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -6646,11 +5891,6 @@
           <t>https://astateqatar.com/</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>54 Otba Bin Mohammed, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6686,11 +5926,6 @@
           <t>http://brightminds-qa.com/</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>8FRP+J82, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -6726,11 +5961,6 @@
           <t>https://galileo-is.com/</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>شارع معيذر الشمالية, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -6766,11 +5996,6 @@
           <t>http://jellyfishnursery.com/</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>7C4W+PQ6, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6806,11 +6031,6 @@
           <t>http://www.littlecambridgenursery.com/</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>733, Zone, Bldg No4, Street, 56 Al Negaiah Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -6846,11 +6066,6 @@
           <t>https://www.ayalna.com/</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>7CH6+9QJ, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6886,11 +6101,6 @@
           <t>http://alreyadahkindergarten.com/</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6926,11 +6136,6 @@
           <t>http://coventrykg.com/</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Talha Bin Khaleed St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6966,11 +6171,6 @@
           <t>https://oxfordschoolqatar.com/</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7006,11 +6206,6 @@
           <t>https://newtonschools.sch.qa/</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Digital Incubation Center, ictQATAR Al-Nasser Tower B, 5th floor, Do</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7046,11 +6241,6 @@
           <t>https://naiseb.com/</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Makkah Al Mukarramah, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7086,11 +6276,6 @@
           <t>https://studycareqatar.com/</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Villa No. 176 &amp; 178, Rawdat Al Khail St Close to Al-Hilal Signal, Do</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7126,11 +6311,6 @@
           <t>https://almaerifahkindergarten.com/</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Eshgab St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7166,11 +6346,6 @@
           <t>https://wwt.qa/</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>25th Floor, Manara, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7206,11 +6381,6 @@
           <t>http://www.ademstravel.com/</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Building: 50, Street:, Lagoona Mall, 51 Zone: 66, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7246,11 +6416,6 @@
           <t>https://www.rotrav.com/</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>185 Bulding 19, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -7286,11 +6451,6 @@
           <t>http://www.blueislandholidays.com/</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>STREET 100 ASIAN TOWNPLAZA MALL SHOP 109, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7326,11 +6486,6 @@
           <t>http://www.lankaexplorer.net/</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>0Palm Towers, Al Funduq St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -7366,11 +6521,6 @@
           <t>http://76adventure.com/</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Umm Ghuwailina zone no 27,Street no950,Building no12,floor 3rd,Offic</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -7406,11 +6556,6 @@
           <t>http://www.flywellholidays.com/</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Al Khalidiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -7446,11 +6591,6 @@
           <t>https://www.eliteescape.co/</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Office Building, Al Mana Plaza, Office 303, 3rd, Qatari Bin Al Fujaa</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -7486,11 +6626,6 @@
           <t>http://www.torchdesertsafaritour.com/</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Industrial Area Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -7561,11 +6696,6 @@
           <t>https://jadwal.qa/</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -7601,11 +6731,6 @@
           <t>https://darwishtravel.com/darwish-united-travels/</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Souq Waqif, Ground floor, Central Inn Hotel, Al Mijdaf St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -7641,11 +6766,6 @@
           <t>https://traveloustour.com/</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -7681,11 +6801,6 @@
           <t>http://kingtravel.qa/</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>King Travels bin mahmoud, Al Jazeera St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -7721,11 +6836,6 @@
           <t>https://365adventures.me/</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Office No. 12, 1st floor, Concord Bldg, Al Rawabi St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -7761,11 +6871,6 @@
           <t>https://www.oatqatar.com/</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>ICONO business center, C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -7801,11 +6906,6 @@
           <t>https://www.qatardeserttour.com/</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>al matar center, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -7841,11 +6941,6 @@
           <t>https://dreamroutetourism.com/</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Building, Flat No 3, Floor 2 Street 950, Zone 27 Building no 64, New</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -7881,11 +6976,6 @@
           <t>https://flytictravelandtours.com/</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Umm Salal Muhammed</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -7921,11 +7011,6 @@
           <t>https://kdtourismqatar.com/</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>119, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -7961,11 +7046,6 @@
           <t>http://www.mkholidaystourism.com/</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>OFFICE NO. 72, 4F ROYAL PLAZA MALL, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -8001,11 +7081,6 @@
           <t>https://www.desertsafariqatar.com/</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>7HX2+55G, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -8041,11 +7116,6 @@
           <t>http://www.inboundtoursqatar.com/</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Concord2, Near Al Rawabi St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -8081,11 +7151,6 @@
           <t>http://www.rehlatytravel.com/</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Al Corniche, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -8121,11 +7186,6 @@
           <t>https://www.safeworldtravels.com/</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Aster Medical Clinic, Near Street 100, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -8161,11 +7221,6 @@
           <t>https://smartwaycab.com/</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>7GJ3+QJ, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -8271,11 +7326,6 @@
           <t>https://www.alghayatours.com/</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Office #26, 2nd Floor, Block F, Al Mirqab Al Jadeed St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -8311,11 +7361,6 @@
           <t>https://desertsafariqtr.com/</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Al Safliya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -8351,11 +7396,6 @@
           <t>https://moondohatravels.com/</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Jasim Bin Hamad St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -8391,11 +7431,6 @@
           <t>https://murexqatartours.com/</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Floor 4, Office 401 Building, 24 Street 940, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -8431,11 +7466,6 @@
           <t>https://bestoftimetourism.com/</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Oryx Business Center, Street 950 Hadat Dallam St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -8471,11 +7501,6 @@
           <t>https://www.myguestsafari.com/</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>2nd floor, Alfardan centre, Grand Hammad St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -8511,11 +7536,6 @@
           <t>https://www.hulooltourism.com/</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>zone,26 . Building, 71 Street,220, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -8551,11 +7571,6 @@
           <t>https://sandscapeadventures.qa/</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Ibn Seena, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -8591,11 +7606,6 @@
           <t>https://qatarholidaysdmc.com/</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Emrair St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -8631,11 +7641,6 @@
           <t>http://www.oceancars.com.qa/</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Zone No.69,Street No.186,Building No.55,Ground floor, Lusail Bouleva</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -8671,11 +7676,6 @@
           <t>https://www.astarlimousineqa.com/</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Elite Trading WLL, Al Rufa Tower/Concord Business Center, 7th Floor</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -8711,11 +7711,6 @@
           <t>http://www.al-naas.com/</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>BIN AJILAN BUILDING, Abu Jubair St, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -8751,11 +7746,6 @@
           <t>http://www.alnabigha.com/</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -8791,11 +7781,6 @@
           <t>https://www.blueflowerqatar.com/</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Zone 42, Stree 280, Building 70 Office 1</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -8831,11 +7816,6 @@
           <t>https://compassqtr.com/</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>building 18, office number 702, Compass Qatar, Rent a Car, Musherib</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -8871,11 +7851,6 @@
           <t>http://www.countryrentacar.com/</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>6H6G+2CQ, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -8911,11 +7886,6 @@
           <t>http://www.dohacab.com/</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -8951,11 +7921,6 @@
           <t>https://mannai.com/activities/automotive/</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Office 06, 2nd Floor, Building 139, Zone 24, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -8991,11 +7956,6 @@
           <t>http://qualitydohagroup.com/</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>6H6F+759, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -9031,11 +7991,6 @@
           <t>https://www.queencarsrentacar.com/</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Al Dalah Building, Al Aziziya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -9071,11 +8026,6 @@
           <t>https://www.selectqatar.com/</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Block 13, 1st Floor, Office, 103 &amp; 104, Sayer Building, East Industr</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -9111,11 +8061,6 @@
           <t>https://greenmotion.com/locations/qatar/doha-downtown</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -9151,11 +8096,6 @@
           <t>http://www.beladyqa.com/</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Al Khaleej St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -9191,11 +8131,6 @@
           <t>https://rent.gulfcar.com/</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Street 24, Al Wakalat Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -9231,11 +8166,6 @@
           <t>https://www.infinity-qatar.com/</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Bin Thani Building, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -9271,11 +8201,6 @@
           <t>http://jnfqatar.com/</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Vertical Circle Ground Floor, Rental Lounge, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -9311,11 +8236,6 @@
           <t>https://peacerentacar.qa/</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>9GX9+7R, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -9351,11 +8271,6 @@
           <t>http://www.skywayqatar.com/</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Al Rabia Building, 138, 1 1 street 362, buiding</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -9391,11 +8306,6 @@
           <t>http://www.strongrentacar.com/</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>7J58+J9Q Hamad international airport, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -9431,11 +8341,6 @@
           <t>https://wellcarelimoqatar.com/</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Office No. 728. Building No. 02. 7th Floor, 7GCF+XX Muntazah Commerc</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -9471,11 +8376,6 @@
           <t>http://www.rentwithdallas.com/</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Omar Al Mukhtar, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -9511,11 +8411,6 @@
           <t>http://www.alaseelhotel.com/</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>55 Al Arab St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -9551,11 +8446,6 @@
           <t>http://www.c-hotelandsuitesdoha.com/</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>District 18, 137 Museum St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -9591,11 +8481,6 @@
           <t>http://www.regencysealinecamp.com/</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>InLand Sea Off Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -9631,11 +8516,6 @@
           <t>https://abraj.com.qa/</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Oqba Bin Nafie St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -9671,11 +8551,6 @@
           <t>http://alnourplaza.qa/</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>8GGF+9P8 Asas Twin Towers, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -9711,11 +8586,6 @@
           <t>https://www.sherao.qa/</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>7GPW+7RM, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -9751,11 +8621,6 @@
           <t>http://www.amgallery.qa/</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Place Vendôme Mall, Gate 5 - 2nd Floor St. Germain, Lusail, Doha, Lu</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -9791,11 +8656,6 @@
           <t>https://artsandcrafts.qa/</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Building No. 04 Al Amal Street, Umm Salal Muhammed, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -9831,11 +8691,6 @@
           <t>https://meraasgallery.com/</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Building 15, Zone 7 (Al Souq), Street, 950 Al Bareed St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -9871,11 +8726,6 @@
           <t>http://www.nouvoinizio.com/</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Fonciere Retaj 1, 820 Al Kinana St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -9911,11 +8761,6 @@
           <t>https://oneaart.com/</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Unit 18, Building, West Walk - Salwa Road, 16 Street 160, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -9951,11 +8796,6 @@
           <t>https://www.premartgallery.com/</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -9991,11 +8831,6 @@
           <t>https://stones.luxury/</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Showroom no. 10, 11, West Walk Building No. 3 Zone 60, Street 810, A</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -10031,11 +8866,6 @@
           <t>http://www.wusumgallery.com/</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>St. Regis Doha Hotel, Al Gassar Resort, Eiwan, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -10071,11 +8901,6 @@
           <t>https://www.iamschoolqatar.com/</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Building 38, Zone, Saad Bin Zura Street, 36 Street 965</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -10111,11 +8936,6 @@
           <t>http://lcqatar.com/</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -10151,11 +8971,6 @@
           <t>http://www.pictureworldqatar.com/</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Umm Şalāl 'Alī</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -10191,11 +9006,6 @@
           <t>https://thegalleryintl.com/</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Building No. 89، Zone 34 Street No. 950, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -10231,11 +9041,6 @@
           <t>http://mjpictorial.com/</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>building number24, 362 rass esharaj, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -10271,11 +9076,6 @@
           <t>https://www.mssky.qa/</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>zone 55 185 zone, 55 Al Aziziya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -10311,11 +9111,6 @@
           <t>https://www.seaplus.qa/</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Lusail Marina, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -10351,11 +9146,6 @@
           <t>http://www.974cruises.com/</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Lusail Marina, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -10391,11 +9181,6 @@
           <t>http://www.sailingplusmegayachts.com/</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>10 La Croisette, Pearl Blvd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -10431,11 +9216,6 @@
           <t>https://gallivantchartersqatar.com/</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Parking Bay S33, Marina Gate 18, Porto Arabia Drive, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -10471,11 +9251,6 @@
           <t>https://www.abcgroupqatar.com/</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Gate Number، A78 Street 41, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -10511,11 +9286,6 @@
           <t>https://glassnhouse.net/</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Street 303, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -10551,11 +9321,6 @@
           <t>http://homeyhomerealestate.com/</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Street 251, Building 63, Second floor, unit 9 Al Amir St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -10591,11 +9356,6 @@
           <t>https://lively-realestate.com/</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Office #294, 29th Floor, Marina, Twin Tower A, Marina Central, Lusai</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -10631,11 +9391,6 @@
           <t>https://www.palmarealestate.qa/</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>7G95+XPP Doha GSSG Building , First floor , Office 6, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -10671,11 +9426,6 @@
           <t>http://stepone.com.qa/</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>7FJW+M6C, Al Difaaf St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -10711,11 +9461,6 @@
           <t>https://www.unlock.com.qa/</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Markaz Almana Building, Old Airport Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -10751,11 +9496,6 @@
           <t>http://alfordhughes.com/</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>6 La Croisette, Porto Arabia The Pearl Qatar 3264, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -10791,11 +9531,6 @@
           <t>http://www.qbayrealestate.com/</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Twin Towers, Tower B, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -10831,11 +9566,6 @@
           <t>https://bluemoonluxuryestates.com/</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Marina Twin Tower B, 13th Floor, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -10871,11 +9601,6 @@
           <t>https://www.regal-realestate.com/</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -10911,11 +9636,6 @@
           <t>https://www.elite-ventureqa.com/</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>B1 - Office no B, Street - 340, Zone 56, Building 299 Gate 1, 104 Sa</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -10951,11 +9671,6 @@
           <t>http://www.threefourrealestate.com/</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>NGT Centre, Othman Bin Affan St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -10991,11 +9706,6 @@
           <t>https://signaturehomesqa.com/</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Zone No:, Building No,72 World Wide Commercial Building Street No: 2</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -11031,11 +9741,6 @@
           <t>http://www.maxam.com.qa/</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Choice Centre, Street 893, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -11071,11 +9776,6 @@
           <t>https://orchidqatar.com/</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>The Pearl Building, Building no 51, Street 310, Airport St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -11111,11 +9811,6 @@
           <t>https://marakkar.qa/</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Jasim Bin Hamad St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -11151,11 +9846,6 @@
           <t>https://studio4.qa/</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>Zone 69 , Building No, Marina 50, 21st Floor, 5 Street No.315, Lusai</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -11191,11 +9881,6 @@
           <t>https://www.artisans.qa/</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Marina twin tower B, 25th Floor, Street 319, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -11231,11 +9916,6 @@
           <t>https://casadekor.online/</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Al Mirqab Al Jadeed St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -11271,11 +9951,6 @@
           <t>http://www.castamo.qa/</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>Building 8 No: 67-68, The Pearl, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -11311,11 +9986,6 @@
           <t>https://homesouq.qa/</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>Building number 43, Street 100,Zone 56</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -11351,11 +10021,6 @@
           <t>https://www.maisoninteriors.qa/</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>230 C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -11391,11 +10056,6 @@
           <t>https://saiffurniture.qa/</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>Wisdom International(Exclusive Office Furniture &amp; Interior Products</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -11431,11 +10091,6 @@
           <t>https://www.safcoqatar.com/</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -11471,11 +10126,6 @@
           <t>https://www.aaadoha.com/</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>5FH5+44Q, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -11511,11 +10161,6 @@
           <t>https://www.omoginteriors.com/</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>Office 70, 2nd Floor, Block E, Al Mirqab Al Jadeed St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -11551,11 +10196,6 @@
           <t>https://www.arara-decor.com/</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>building 36, floor 1, office 1, Street 989 Al Shafi Street، Al-Rayya</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -11591,11 +10231,6 @@
           <t>https://www.brymaxlighting.com/</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>Building 136, Zone, Shop No: 9 and 10, 71 Street 750, Umm Salal Muha</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -11631,11 +10266,6 @@
           <t>https://www.chimneyworld.com/</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -11671,11 +10301,6 @@
           <t>https://www.conmarbledesign.com/</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>Regus Business Center, Piazza Level, QQ05A, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -11711,11 +10336,6 @@
           <t>http://www.luxuryhome-qa.com/</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>Salwa Road, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -11751,11 +10371,6 @@
           <t>https://dohapm.com/</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>Office 254, 9GPF+RC7 Twin Towers, Tower B, 25th Floor, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -11791,11 +10406,6 @@
           <t>http://www.foscstudio.com/</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>Al Nasr Tower A, Al Markhiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -11831,11 +10441,6 @@
           <t>https://www.ghadeerid.com/</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>Al Jazera Al Arabia Street Al Hattab Holding HQ2 Near Doha Police cl</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -11871,11 +10476,6 @@
           <t>https://www.heaven-stone.com/</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>P.O. Box 35136, Salwa Road, Doha, Qatar, Al Muntazah, Doha 35136</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -11911,11 +10511,6 @@
           <t>https://kbrcgulf.com/</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>Palm Tower B, 15th floor, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -11951,11 +10546,6 @@
           <t>https://levantekitchens.com/</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>7F2F+9J, Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -11991,11 +10581,6 @@
           <t>https://mavendesignqa.com/</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>Building 108, Burj marina tower, Street 303, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -12031,11 +10616,6 @@
           <t>https://jascoqatar.com/</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>3110 Building No: 19, Street 3110, Birkat Al Awamer</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -12071,11 +10651,6 @@
           <t>https://www.nabcostore.com/</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>Al Shamal Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -12111,11 +10686,6 @@
           <t>http://pasostudios.com/</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>9GQF+RC6, Street 305 Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -12151,11 +10721,6 @@
           <t>https://redvelvetqa.com/</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>Salwa Road, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -12191,11 +10756,6 @@
           <t>http://www.sendianpaints.com/</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>Hazm Al Markhiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -12231,11 +10791,6 @@
           <t>https://starkitchenequipments.com/</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>St 990, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -12271,11 +10826,6 @@
           <t>http://topqqatar.com/</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>Office No.74, E Block 2nd Floor, Al Mirqab Mall, Street 840, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -12311,11 +10861,6 @@
           <t>https://vexel-group.com/</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>Zone 24 ,Building number 12, Building Number 7, Muntazaah commercial</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -12351,11 +10896,6 @@
           <t>https://almuftah.com/what-we-do/lifestyle/almuftah-furniture-decoration/</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>Al Ain Complex, Building 349, Unit No.6, 340 Al Muntazah, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -12391,11 +10931,6 @@
           <t>https://www.glaze.qa/</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>zone 56, bldg، 189 Street 995, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -12431,11 +10966,6 @@
           <t>http://www.asianpaintsarabia.com/</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>Ain Khaled St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -12471,11 +11001,6 @@
           <t>https://indecor.qa/</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>Zone 91, Building, 58 Street 3119, Birkat Al Awamer</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -12511,11 +11036,6 @@
           <t>http://www.starcarqa.com/</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>Tyseer service center، Inside old airport, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -12551,11 +11071,6 @@
           <t>http://www.bradran-persian-carpets.com/</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>Unnamed Road, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -12591,11 +11106,6 @@
           <t>https://classinteriordecoration.com/</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>2nd floor, Al Dihailiyat street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -12631,11 +11141,6 @@
           <t>https://qatarsofaupholstery.com/</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>226, 56 Jery Saleh St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -12671,11 +11176,6 @@
           <t>http://curtaincarpet.com/</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -12711,11 +11211,6 @@
           <t>http://www.liwanfurniture.com/</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>SHOP NO F 11-14 , Tawarmall, 1St FLOOR, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -12751,11 +11246,6 @@
           <t>https://sofaupholsteryqatar.com/</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>869, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -12861,11 +11351,6 @@
           <t>http://www.alhussainialuminium.qa/</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -12901,11 +11386,6 @@
           <t>https://gossy.qa/</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>52 Al Rayyan Al Jadeed St, Ar Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -12941,11 +11421,6 @@
           <t>https://silvercoast.qa/</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>9C2H+WM8, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -12981,11 +11456,6 @@
           <t>https://www.azureqatar.com/</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>Office No.3, Building No.37, Zone, 43 Street No.701, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -13021,11 +11491,6 @@
           <t>http://delmonqa.com/</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>7F3M+WGR Al Falah Center, Salwa Rd Street No 340, Zone No 56, Buildi</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -13061,11 +11526,6 @@
           <t>http://www.espacioqatar.com/</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -13101,11 +11561,6 @@
           <t>https://www.infinitymarbledesign.com/</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>180 Othman Bin Affan St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -13141,11 +11596,6 @@
           <t>https://qatar.optionscarpentry.com/</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>Street N, Ar-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -13181,11 +11631,6 @@
           <t>https://www.rimka-group.com/</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>luciano@latinotype.com, info@rimka-group.com</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -13221,11 +11666,6 @@
           <t>https://rivieragardens-qa.com/</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>9F29+49M, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -13261,11 +11701,6 @@
           <t>http://www.swaqatar.com/</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -13301,11 +11736,6 @@
           <t>http://uarc.net/</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>Nuaija, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -13341,11 +11771,6 @@
           <t>http://vividusinterior.com/</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>Wadi Musheirib St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -13381,11 +11806,6 @@
           <t>https://www.colorsqatar.com/</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>Industrial Area, Qatar · Doha, Qatar ·, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -13421,11 +11841,6 @@
           <t>https://oppeinqatar.com/</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>7F2C+678 West Walk - Salwa Road, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -13461,11 +11876,6 @@
           <t>https://www.aurexgroup.qa/</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -13501,11 +11911,6 @@
           <t>https://decolite.co/</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>Al Aziziyah, Al Harith Bin Hisham St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -13541,11 +11946,6 @@
           <t>http://interprogetti.qa/</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>Marina - South, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -13581,11 +11981,6 @@
           <t>https://nabni.qa/</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>Sadia Burger Building, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -13621,11 +12016,6 @@
           <t>http://www.attqatar.com/</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>Arkan Building, Block No. 6, Barwa Commercial Ave, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -13661,11 +12051,6 @@
           <t>http://www.brandscapefitout.com/</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>Office 22, Floor 2, Bldg. 191, Wholesale Market, 995 St St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -13701,11 +12086,6 @@
           <t>https://www.jatconqa.com/</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>World Wide Commercial Building, Building 72, Street 250, D Ring Rd</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -13741,11 +12121,6 @@
           <t>http://www.libratradingcompany.com/</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>Souq Mall, HUB Business Center, 2nd Floor, Al Mirqab Al Jadeed St, D</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -13781,11 +12156,6 @@
           <t>http://www.cityelevators.com/</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>Z-45, Old Airport B-212, St-310, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -13821,11 +12191,6 @@
           <t>http://www.sectiontrading.com/</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>7GH5+764, C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -13861,11 +12226,6 @@
           <t>https://utccqatar.com/</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>Office No. 8, 4th Floor, Building No. 26 Street 880, روضة الخيل، Doh</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -13901,11 +12261,6 @@
           <t>https://vertexhygiene.com/</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -13941,11 +12296,6 @@
           <t>https://www.volar.qa/</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>Bld No - 335, St no - 340, Zone, opposite to KFC, 56 Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -13981,11 +12331,6 @@
           <t>https://www.jupiter-qa.com/</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>9CXF+4VG, Al Kharaitiyat N Rd, Umm Salal Muhammed</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -14021,11 +12366,6 @@
           <t>https://nbccqatar.com/</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>Al Rehab Street, Salwa Rd</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -14061,11 +12401,6 @@
           <t>http://www.shareefaconstruction.com/</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>Al aziziya street، شارع الجزيرة العربية, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -14101,11 +12436,6 @@
           <t>http://walkingpad.qa/</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>Shop No.12, Building 44, Retaj Al Waab Building, Zone 55 Street 162</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -14141,11 +12471,6 @@
           <t>http://www.all.design/</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>Marina 50 Tower 18th Floor Lusail City</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -14216,11 +12541,6 @@
           <t>https://interiorcarpentryqatar.com/</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>Birkat Al Awamer</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -14256,11 +12576,6 @@
           <t>https://qatarflmservices.com/</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>Building 45, Street 850, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -14366,11 +12681,6 @@
           <t>https://lecadeau.qa/</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>Al Mirqab Tower, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -14406,11 +12716,6 @@
           <t>https://momentummedia.qa/</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>1st floor, Office no 104, Markaz Almana, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -14446,11 +12751,6 @@
           <t>http://www.multiflow.qa/</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>ZONE :, All MISHAAL COMMERCIAL CENTER, MULTIFLOW TRADING OFFICE No :</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -14486,11 +12786,6 @@
           <t>http://www.add-wells.com/</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>Office 2, Street 230, Zone 27, Building, Ezdan Building 3 Ground flo</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -14526,11 +12821,6 @@
           <t>https://www.digitaltwinqatar.com/</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>Office number 7, Ground floor, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -14566,11 +12856,6 @@
           <t>http://www.exelgraphics.com/</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>Al Wakrah Rd Barwa village Building No.11- Shop No.47 924, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -14606,11 +12891,6 @@
           <t>https://www.genesis-qatar.com/</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>Office L3, 4th Floor, Al Hitmi Building, C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -14646,11 +12926,6 @@
           <t>https://happetoys.com/</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>Building No: 57 Zone: 45 Street:, 7H42+WF7 Al Kazim Building, 250 D</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -14686,11 +12961,6 @@
           <t>https://www.imprimotrading.com/</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>5th Floor , Marina 50, Street No.315, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -14726,11 +12996,6 @@
           <t>http://www.moodhamper.com/</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>7GPJ+5CF, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -14766,11 +13031,6 @@
           <t>http://www.premadasaprintsolutions.com/</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>Wholesale Market St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -14806,11 +13066,6 @@
           <t>https://duplexpack.com/</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -14846,11 +13101,6 @@
           <t>https://forall.qa/</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>7F22+9WC, Osama Bin Zaid St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -14886,11 +13136,6 @@
           <t>http://www.giftcityqatar.com/</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>280 Zone 55 Building Number 541, Ground Floor, Office Number 2</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -14926,11 +13171,6 @@
           <t>https://lineartprinting.com/</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>Building 659، Asian town Cricket Stadium Shop no 21 ZONE، 56 Street</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -14966,11 +13206,6 @@
           <t>https://www.myoffice.qa/</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>Zone 44,Street:, Building No:-249, 330 Rawdat Al Khail St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -15006,11 +13241,6 @@
           <t>https://www.shinegd.com/</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>Al Ashat Street Gold Souq, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -15046,11 +13276,6 @@
           <t>https://www.decarloqatar.com/</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>Ezdan palace Hotel, zone 31 street 850 building 251, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -15086,11 +13311,6 @@
           <t>https://www.fitwell.qa/</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>http://www.google.com/maps/place/25.328461,51.452714, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -15126,11 +13346,6 @@
           <t>http://sketchdoha.com/</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>Building #12 office, 1 Al Ikhaa St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -15166,11 +13381,6 @@
           <t>https://packandprint.qa/</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>58, Zone 91, Street 3088 Birkat Al Awameer, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -15206,11 +13416,6 @@
           <t>https://printhouse.qa/</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>Building No: 74, Street No: 3144, Birkat Al Awamer</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -15246,11 +13451,6 @@
           <t>https://www.addon-it.net/</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>Badriya Signal, Al Jazeera St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -15286,11 +13486,6 @@
           <t>https://macawsqatar.com/</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>Al Wakra Main service St, Al Wakrah</t>
-        </is>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -15326,11 +13521,6 @@
           <t>http://oryxprinting.com/</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>Street No: 5, Building No: 84, Zone :81, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -15366,11 +13556,6 @@
           <t>https://www.packagingheights.com/</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>50 Qatari Bin Al Fujaah St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -15406,11 +13591,6 @@
           <t>https://pixeladvt.com/</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>Ezdan Oasis, Gate 6, Land D, Building no A44 Street 5, Al Wukair</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -15446,11 +13626,6 @@
           <t>http://www.printzoneqa.com/</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -15486,11 +13661,6 @@
           <t>http://www.warqqa.com/</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>4CF3+JV3, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -15526,11 +13696,6 @@
           <t>https://printhouseqa.com/</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>Zone 22, Building، Street 342، 4 Al Jazeera St</t>
-        </is>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -15566,11 +13731,6 @@
           <t>http://www.forwardgroup.qa/</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>Office - 2, Building, 208 Street - Rawdat Al Khail, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -15606,11 +13766,6 @@
           <t>http://fido.qa/</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>Ibn Aslam St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -15646,11 +13801,6 @@
           <t>https://followme.qa/</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>STREET 319, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -15686,11 +13836,6 @@
           <t>https://gingertechnologies.qa/</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>Musherib Building، Zone: 14, Street 905 Bldg. No: 5, Al Jazeera St</t>
-        </is>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -15726,11 +13871,6 @@
           <t>https://impakt.qa/</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>Al Mirqab Al Jadeed St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -15766,11 +13906,6 @@
           <t>https://inline.qa/</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>Wholesale Market St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -15806,11 +13941,6 @@
           <t>https://lamlan.qa/</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>Al Jazeera Tower, Conference Centre, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -15846,11 +13976,6 @@
           <t>https://multimedia.qa/</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>Zone 51, Building, 164 Street 950, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -15886,11 +14011,6 @@
           <t>http://www.nasher.qa/</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>Building No 14, Jaber Bin Mohd St, Street No 109, Zoon No 7, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -15926,11 +14046,6 @@
           <t>https://speedlinemedia.qa/</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>Room no: 601 Aqar Building 6th Floor, Badriya Signal, Al Jazeera St</t>
-        </is>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -15966,11 +14081,6 @@
           <t>https://www.taqnia.qa/</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>167 Al Rayan Plaza. St 150 4th Floor, Office 406</t>
-        </is>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -16006,11 +14116,6 @@
           <t>https://5d-ads.com/</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>Office Number 18, Abu Hamour Complex, Building 191, Street 995, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -16046,11 +14151,6 @@
           <t>https://www.adonaisolutions.org/</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -16086,11 +14186,6 @@
           <t>http://www.dgtalcyberkoms.com/</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>WS 95, HUB Business Center, Royal Plaza Mall, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -16126,11 +14221,6 @@
           <t>https://dezignix.com/</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>Office 36, 8th Floor, Hleyton Tower, Al Corniche, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -16166,11 +14256,6 @@
           <t>https://inboundhype.com/</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>7GJ4+FX, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -16206,11 +14291,6 @@
           <t>https://www.semlion.com/</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>945 Jaww Fehaiheel St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -16246,11 +14326,6 @@
           <t>https://www.doodlebrand.com/</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>Building No: 210, 43 Nuaija, 330 Rawdat Al Khail St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -16286,11 +14361,6 @@
           <t>http://www.eclipsemediaqa.com/</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>4th Floor , Office, Pearl Tower, 310, 404 Al Matar service St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -16326,11 +14396,6 @@
           <t>https://www.everprintqatar.com/</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>Floor no 1, Building no 94, Zone 25, Street 850, Mansoura street, Fl</t>
-        </is>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -16366,11 +14431,6 @@
           <t>http://flexmediaqa.com/</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr">
-        <is>
-          <t>Al Markhiya Street, Al Jaber square Building - Doha Second floor - O</t>
-        </is>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -16406,11 +14466,6 @@
           <t>http://www.formacreative.co/</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>Al Emadi Financial Square Building 2, Office 6, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -16446,11 +14501,6 @@
           <t>https://naseebku.com/</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>Zone 18, Near Zaithoon, 840 Al Aaliya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -16486,11 +14536,6 @@
           <t>https://huesgraphics.com/</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>Tornado Tower, Majlis Al Taawon St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -16526,11 +14571,6 @@
           <t>https://inhanddesignqatar.com/</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>Office No. 8, Third Floor, Old Al Mana Building, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -16566,11 +14606,6 @@
           <t>http://www.kingadqatar.com/</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr">
-        <is>
-          <t>Al Wakra Main St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -16606,11 +14641,6 @@
           <t>https://lineagency.me/</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>26mix marina, Union Trust Tower, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -16646,11 +14676,6 @@
           <t>https://lbgdigitalmarketingcompanyqatar.com/</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>31 Umm Ghuwailina St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -16686,11 +14711,6 @@
           <t>https://www.lumiere-qa.com/</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr">
-        <is>
-          <t>7F7X+JHX, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -16726,11 +14746,6 @@
           <t>http://www.mediacraftqatar.com/</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr">
-        <is>
-          <t>Building No. 53, Street 76 SAEEB BIN BASHEER، Rasheeda Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -16766,11 +14781,6 @@
           <t>https://www.nah4media.net/</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -16806,11 +14816,6 @@
           <t>https://psastech.com/</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>Office # 214-215, Floor # 2, Regus Business Centre, No. 65, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -16846,11 +14851,6 @@
           <t>http://ptcmediaqatar.com/</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>PTC Media، Post Box 30193, Room No: A -159, Retaj Building No: 4 Nea</t>
-        </is>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -16886,11 +14886,6 @@
           <t>https://qa.prosignsglobal.com/</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>Al Matar Center Parking, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -16926,11 +14921,6 @@
           <t>https://digisolutionsqa.com/</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>Office No.302, Floor 3, Corniche Promenade, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -16966,11 +14956,6 @@
           <t>http://q-discounts.com/</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>Al-Kuwari Complex, Premier Infotech, 2nd floor, BIN JAHAM, Al Ghotah</t>
-        </is>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -17006,11 +14991,6 @@
           <t>https://www.qsbtechnologies.com/</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>Building No 58, 1st Floor, Office, 3 Grand Hammad St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -17046,11 +15026,6 @@
           <t>https://qatarclick.com/</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>building 56, 56 Al Jazeera St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -17086,11 +15061,6 @@
           <t>https://www.qatardigitals.com/</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>7GMV+PW8, Al Dostour St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -17126,11 +15096,6 @@
           <t>http://www.ramiproductions.com/</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>Al Bustan Center, 4th Floor , 403A, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -17166,11 +15131,6 @@
           <t>https://www.reva.solutions/</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>Al Mirqab Mall, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -17206,11 +15166,6 @@
           <t>http://www.signatureadvertisers.com/</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>5CQP+P5C, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -17246,11 +15201,6 @@
           <t>http://spark-house.com/</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>Office No. 3, 304 Al Matar Al Qadeem St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -17286,11 +15236,6 @@
           <t>http://specra.co/</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>Street 420, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -17326,11 +15271,6 @@
           <t>https://www.thesketch.agency/</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -17366,11 +15306,6 @@
           <t>http://www.spectrumagency.co/</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>6HHX+XM8 Business Innovation Park - QFZA, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -17406,11 +15341,6 @@
           <t>https://www.vmsqa23.com/</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>931, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -17446,11 +15376,6 @@
           <t>http://www.vraxa.com/</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>Westbay, Qatar, Lagoona Mall, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -17486,11 +15411,6 @@
           <t>http://www.walkeranddavies.com/</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>7F2C+2XQ, Rumaillah Group, Salwa Road, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -17526,11 +15446,6 @@
           <t>http://www.zenoids.com/qatar</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr">
-        <is>
-          <t>Mannai Accomadation, Building No:25, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -17601,11 +15516,6 @@
           <t>https://marketingdesign.agency/</t>
         </is>
       </c>
-      <c r="H431" t="inlineStr">
-        <is>
-          <t>820, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -17641,11 +15551,6 @@
           <t>https://qadvertising.qa/</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr">
-        <is>
-          <t>عقار رقم ٢٠٨، شارع رقم ٣٣٠، منطقة ٤٣،, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -17681,11 +15586,6 @@
           <t>https://brillcreations.com/</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>Brill Creations، POB 214096، 2nd Floor, Office No. 1, Al Matar Centr</t>
-        </is>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -17721,11 +15621,6 @@
           <t>https://eyebeedigital.com/</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>2nd Floor Office Number 208,Building Number 08 Street 840, Ace Busin</t>
-        </is>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -17761,11 +15656,6 @@
           <t>https://silverfox.qa/</t>
         </is>
       </c>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>Palm Tower B - 18th Floor, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -17801,11 +15691,6 @@
           <t>https://trionix.qa/</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr">
-        <is>
-          <t>Zone No, Building No 28, 220 B Ring Road, 16 Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -17841,11 +15726,6 @@
           <t>http://spirexagency.com/</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -17881,11 +15761,6 @@
           <t>https://swafaunais.com/</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>851 Al Matar Al Qadeem St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -17921,11 +15796,6 @@
           <t>https://aadilmajeed.com/</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>Opposite Indian Coffee House, B Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -17961,11 +15831,6 @@
           <t>http://www.gulfneon.net/</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>Blg-86, St-220,Zone -15, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -18001,11 +15866,6 @@
           <t>https://www.mindomega.com/</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>Street 915, Zone 47, El Ekresh, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -18041,11 +15901,6 @@
           <t>https://xzmeeraj.com/</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>gharaffah, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -18151,11 +16006,6 @@
           <t>https://www.primeshop.qa/</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>Najma, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -18191,11 +16041,6 @@
           <t>https://www.vortex.qa/</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>Office No 104, 146 Ibn Seena, 3rd Floor, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -18231,11 +16076,6 @@
           <t>https://www.akinsadvertising.com/</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>4th Floor , 403, A , Al Bustan Center, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -18271,11 +16111,6 @@
           <t>https://www.akinsglobal.com/</t>
         </is>
       </c>
-      <c r="H448" t="inlineStr">
-        <is>
-          <t>Building No 43, Fujigrand, Floor 2, Apartment 251, Zone, 56 Street 1</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -18311,11 +16146,6 @@
           <t>https://www.fantazyaland.com/</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>Street 41, Ar-Rayyan, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -18351,11 +16181,6 @@
           <t>http://www.jbaagency.net/</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>Street 920, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -18391,11 +16216,6 @@
           <t>https://www.jblads.com/</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>Office No. 251, Souq Al Naif, Floor Street 2, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -18431,11 +16251,6 @@
           <t>https://www.justjusticeqa.com/</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>Mirqab Mall, 3rd Floor, Al Amir St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -18471,11 +16286,6 @@
           <t>http://www.newsmartsolution.com/</t>
         </is>
       </c>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>Building no 139 Rawdat Al Khail, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -18511,11 +16321,6 @@
           <t>http://www.picawagroup.com/</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr">
-        <is>
-          <t>Zone 55, Building, 458 Street 280, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -18551,11 +16356,6 @@
           <t>https://www.rebrandsign.com/</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>Building No- 282, Ezdan Oasis, Shop No, 3 D-Block, Al Wakrah</t>
-        </is>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -18591,11 +16391,6 @@
           <t>https://tgemqatar.com/</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr">
-        <is>
-          <t>Regus Al Jaidah Business Center, Office, 207 D Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -18631,11 +16426,6 @@
           <t>https://www.yaracompany.com/</t>
         </is>
       </c>
-      <c r="H457" t="inlineStr">
-        <is>
-          <t>The Pearl, Tower 121</t>
-        </is>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -18671,11 +16461,6 @@
           <t>https://folaim.com/</t>
         </is>
       </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>Street 303, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -18711,11 +16496,6 @@
           <t>https://motivedesigns.net/</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr">
-        <is>
-          <t>Al rabea 1 building, madinat Khalifa S, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -18751,11 +16531,6 @@
           <t>https://fingerprint.qa/</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -18791,11 +16566,6 @@
           <t>https://www.marsamadv.com/</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr">
-        <is>
-          <t>Al Amir St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -18831,11 +16601,6 @@
           <t>https://mediacenter.qa/</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr">
-        <is>
-          <t>920, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -18871,11 +16636,6 @@
           <t>http://www.qonnect.qa/</t>
         </is>
       </c>
-      <c r="H463" t="inlineStr">
-        <is>
-          <t>Office No. 29, Second Floor, Building, 123 Street 362, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -18911,11 +16671,6 @@
           <t>http://shinegroup.qa/</t>
         </is>
       </c>
-      <c r="H464" t="inlineStr">
-        <is>
-          <t>148 Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -18951,11 +16706,6 @@
           <t>http://www.lexafilms.com/</t>
         </is>
       </c>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>M7 Doha, M7</t>
-        </is>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -18991,11 +16741,6 @@
           <t>https://www.mediasquare.tv/</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr">
-        <is>
-          <t>Dohatna Logistics Park-Umm Shaharaine1 (Warehouses &amp; Logistics, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -19031,11 +16776,6 @@
           <t>https://mediastreamproduction.com/</t>
         </is>
       </c>
-      <c r="H467" t="inlineStr">
-        <is>
-          <t>The, Pearl Blvd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -19071,11 +16811,6 @@
           <t>https://olympiaarabia.com/photography-services/</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr">
-        <is>
-          <t>Al Nasr Family Food Centre Opposite</t>
-        </is>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -19111,11 +16846,6 @@
           <t>https://www.qsgqatar.com/</t>
         </is>
       </c>
-      <c r="H469" t="inlineStr">
-        <is>
-          <t>Bldg No:36 Global Business Center, Zone:27 Street: 230, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -19151,11 +16881,6 @@
           <t>http://www.recordonstudio.com/</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr">
-        <is>
-          <t>Al Madina, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -19191,11 +16916,6 @@
           <t>http://tfsch.com/</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr">
-        <is>
-          <t>Office #10, Nasrullah Complex, Al Ghafiqi St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -19231,11 +16951,6 @@
           <t>https://www.talenthubdoha.com/</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr">
-        <is>
-          <t>Office: 410 ,Floor: 4,Building no: 103 ,Zone: 38, Street: 231, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -19271,11 +16986,6 @@
           <t>https://unltddevice.com/</t>
         </is>
       </c>
-      <c r="H473" t="inlineStr">
-        <is>
-          <t>SFS: 082 Building No: 35, The commercial avenue, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -19311,11 +17021,6 @@
           <t>http://zen-production.com/</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr">
-        <is>
-          <t>Marina, lusail Marina, the e18hteen tower Lusail, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -19351,11 +17056,6 @@
           <t>https://wehostx.com/</t>
         </is>
       </c>
-      <c r="H475" t="inlineStr">
-        <is>
-          <t>Burj Marina Tower, Unit 1 Ground Floor, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -19426,11 +17126,6 @@
           <t>https://alaa.qa/</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr">
-        <is>
-          <t>7CP9+PX, Al Shafi, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -19466,11 +17161,6 @@
           <t>https://almanastudio.com/</t>
         </is>
       </c>
-      <c r="H478" t="inlineStr">
-        <is>
-          <t>Tornado Tower 17, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -19541,11 +17231,6 @@
           <t>https://www.bagerhatcar.com/</t>
         </is>
       </c>
-      <c r="H480" t="inlineStr">
-        <is>
-          <t>Thani Bin Jasim St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -19581,11 +17266,6 @@
           <t>https://adinsaflowers.com/</t>
         </is>
       </c>
-      <c r="H481" t="inlineStr">
-        <is>
-          <t>Al Gharafa Complex, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -19621,11 +17301,6 @@
           <t>http://www.brilliance.org/</t>
         </is>
       </c>
-      <c r="H482" t="inlineStr">
-        <is>
-          <t>Al Waab St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -19661,11 +17336,6 @@
           <t>http://www.skyvisionadv.com/</t>
         </is>
       </c>
-      <c r="H483" t="inlineStr">
-        <is>
-          <t>Al Meena St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -19701,11 +17371,6 @@
           <t>http://www.andalusia.qa/</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr">
-        <is>
-          <t>Al Luqta St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -19741,11 +17406,6 @@
           <t>http://www.atozetc.com/</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>Unit 5, Building 177, Street 340, Al Muntazah, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -19781,11 +17441,6 @@
           <t>https://theexpoqatar.com/</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr">
-        <is>
-          <t>Office Number 16, Hub Business Centre, Barwa Commercial Avenue Build</t>
-        </is>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -19821,11 +17476,6 @@
           <t>http://www.oxygenqr.com/</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>330 Rawdat Al Khail St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -19861,11 +17511,6 @@
           <t>http://www.massprome.com/</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr">
-        <is>
-          <t>Al Jazira Al Arabiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -19901,11 +17546,6 @@
           <t>https://www.geolore.co/</t>
         </is>
       </c>
-      <c r="H489" t="inlineStr">
-        <is>
-          <t>Floor 16, Tornado Tower 17, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -19941,11 +17581,6 @@
           <t>https://grayeventsqatar.com/</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr">
-        <is>
-          <t>Zone 69 Building, A2B Street 215, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -19981,11 +17616,6 @@
           <t>https://www.highlevel-events.com/</t>
         </is>
       </c>
-      <c r="H491" t="inlineStr">
-        <is>
-          <t>Royal Plaza 3rd Floor, Al Sadd St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -20021,11 +17651,6 @@
           <t>http://symphonydoha.com/</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr">
-        <is>
-          <t>STREET 3029 BIRKAT AL AWAMER، الوكير</t>
-        </is>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -20061,11 +17686,6 @@
           <t>https://arceve.qa/</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr">
-        <is>
-          <t>Street 250, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -20101,11 +17721,6 @@
           <t>https://altoproductions.qa/</t>
         </is>
       </c>
-      <c r="H494" t="inlineStr">
-        <is>
-          <t>Building No:20, Street: 940, 26 Najma, Floor 1, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -20141,11 +17756,6 @@
           <t>https://whitecrownqa.com/</t>
         </is>
       </c>
-      <c r="H495" t="inlineStr">
-        <is>
-          <t>4, Floor 3, Bldg.64, Zone, Office, 27 Umm Ghuwailina St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -20181,11 +17791,6 @@
           <t>http://www.dct.com.qa/</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t>Avenue, Barwa Alsadd، Arafat Business Center, Suhaim bin Hamad, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -20221,11 +17826,6 @@
           <t>http://www.teknomedia.qa/</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t>Al-Kuwari Complex, Premier Teknomedia Office No: 23, 2nd Floor Build</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -20261,11 +17861,6 @@
           <t>https://www.rnaqatar.com/</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr">
-        <is>
-          <t>R31 2nd floor, Icon view, office, C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -20371,11 +17966,6 @@
           <t>http://www.mstqatar.com/</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t>Zone 57, Building No, 136 Street 37, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -20411,11 +18001,6 @@
           <t>http://www.alalistrading.com/</t>
         </is>
       </c>
-      <c r="H502" t="inlineStr">
-        <is>
-          <t>Omar Bin Khattab St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -20451,11 +18036,6 @@
           <t>https://www.tuluflorals.com/</t>
         </is>
       </c>
-      <c r="H503" t="inlineStr">
-        <is>
-          <t>TAWAR MALL, Al Markhiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -20491,11 +18071,6 @@
           <t>http://www.sportsvillageqatar.com/</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr">
-        <is>
-          <t>New Industrial Area, Street No. 3, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -20531,11 +18106,6 @@
           <t>http://gemtqatar.com/</t>
         </is>
       </c>
-      <c r="H505" t="inlineStr">
-        <is>
-          <t>Zone -56 Shop Number - 63, Souq Al Nayif, Building Number- 43, Stree</t>
-        </is>
-      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -20571,11 +18141,6 @@
           <t>http://www.qstardoha.com/</t>
         </is>
       </c>
-      <c r="H506" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -20611,11 +18176,6 @@
           <t>https://www.ampsqr.com/</t>
         </is>
       </c>
-      <c r="H507" t="inlineStr">
-        <is>
-          <t>Building no 30, Street 294, Wakara</t>
-        </is>
-      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -20651,11 +18211,6 @@
           <t>https://falconaircondition.com/</t>
         </is>
       </c>
-      <c r="H508" t="inlineStr">
-        <is>
-          <t>RM.902, MUSHEIREB OFFICE TOWER 9TH FL AHMED BIN MOHAMMED BIN THANI S</t>
-        </is>
-      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -20691,11 +18246,6 @@
           <t>http://www.dohaplastichouse.com/</t>
         </is>
       </c>
-      <c r="H509" t="inlineStr">
-        <is>
-          <t>old al ghanim old al ghanem, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -20731,11 +18281,6 @@
           <t>https://www.amsterinternational.com/</t>
         </is>
       </c>
-      <c r="H510" t="inlineStr">
-        <is>
-          <t>Street No. 930, Zone 53, Building No. 36 Office No. 20, 2nd Floor, A</t>
-        </is>
-      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -20771,11 +18316,6 @@
           <t>http://www.almalitha.com/</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr">
-        <is>
-          <t>Al Muaither St, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -20811,11 +18351,6 @@
           <t>https://akazsportshub.com/</t>
         </is>
       </c>
-      <c r="H512" t="inlineStr">
-        <is>
-          <t>zone 47 building no 3, Street 994, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -20851,11 +18386,6 @@
           <t>https://controlqatar.com/</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr">
-        <is>
-          <t>Building No. 11, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -20891,11 +18421,6 @@
           <t>https://moonatbinshaheentrading.com/</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr">
-        <is>
-          <t>SHOP NO:, SOUQ HARAJ, 124 GATE 4, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -20931,11 +18456,6 @@
           <t>http://www.qatarwears.com/</t>
         </is>
       </c>
-      <c r="H515" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -20971,11 +18491,6 @@
           <t>http://www.moonmed.qa/</t>
         </is>
       </c>
-      <c r="H516" t="inlineStr">
-        <is>
-          <t>Zone 56 Building, Salwa Road, 340 Street, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -21011,11 +18526,6 @@
           <t>http://www.aqualeena.com/</t>
         </is>
       </c>
-      <c r="H517" t="inlineStr">
-        <is>
-          <t>Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -21051,11 +18561,6 @@
           <t>http://greatcaretcs.com/</t>
         </is>
       </c>
-      <c r="H518" t="inlineStr">
-        <is>
-          <t>Shop No. 4, Thursday Friday Souq, Building No. 6, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -21091,11 +18596,6 @@
           <t>http://musclebuildqatar.com/</t>
         </is>
       </c>
-      <c r="H519" t="inlineStr">
-        <is>
-          <t>484 Salwa Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -21131,11 +18631,6 @@
           <t>http://www.brouqtrading.com/</t>
         </is>
       </c>
-      <c r="H520" t="inlineStr">
-        <is>
-          <t>Al Jazeera St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -21171,11 +18666,6 @@
           <t>https://www.foodbizqa.com/</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr">
-        <is>
-          <t>Zone 24, Floor, 6 Street 830, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -21211,11 +18701,6 @@
           <t>http://www.alsadanh.com/</t>
         </is>
       </c>
-      <c r="H522" t="inlineStr">
-        <is>
-          <t>Ain Khaled St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -21251,11 +18736,6 @@
           <t>https://www.sassitrade.com/</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr">
-        <is>
-          <t>Al Mirqab Mall, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -21291,11 +18771,6 @@
           <t>https://www.acongulf.com/</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -21331,11 +18806,6 @@
           <t>https://aljazeeraqatar.com/</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -21371,11 +18841,6 @@
           <t>http://concordqatar.qa/</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
-        <is>
-          <t>Shop No:24, Building No:6, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -21446,11 +18911,6 @@
           <t>https://matrixxoverseas.com/qatar</t>
         </is>
       </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>Sharq plaza Building, office, 109 D Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -21486,11 +18946,6 @@
           <t>http://www.alahadgroup.com/</t>
         </is>
       </c>
-      <c r="H529" t="inlineStr">
-        <is>
-          <t>Al Asmakh St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -21526,11 +18981,6 @@
           <t>https://officialmanpower.com/</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
-        <is>
-          <t>Al Mana Twin Towers, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -21566,11 +19016,6 @@
           <t>https://alsalehmanpower.com/</t>
         </is>
       </c>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>Street، 119 Grand Hammad St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -21606,11 +19051,6 @@
           <t>https://www.lhrsgroup.com/</t>
         </is>
       </c>
-      <c r="H532" t="inlineStr">
-        <is>
-          <t>304, 3rd Floor, MKM Tower, Emrair St, Al Corniche, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -21646,11 +19086,6 @@
           <t>http://www.ilmeducationconsultants.com/</t>
         </is>
       </c>
-      <c r="H533" t="inlineStr">
-        <is>
-          <t>267 D Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -21686,11 +19121,6 @@
           <t>https://www.feamishqatar.com/</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr">
-        <is>
-          <t>National Museum of Qatar, 1305, 13th Floor, Gitco Tower, Building No</t>
-        </is>
-      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -21726,11 +19156,6 @@
           <t>https://gb2bnetwork.com/</t>
         </is>
       </c>
-      <c r="H535" t="inlineStr">
-        <is>
-          <t>World Wide Commercial Building, 1st Floor, D Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -21766,11 +19191,6 @@
           <t>https://www.mapstrdg.com/index.html</t>
         </is>
       </c>
-      <c r="H536" t="inlineStr">
-        <is>
-          <t>Opp.Alfardan automobiles, 6CCP+3M7 Doha, Qatar Al Nayef souq, East I</t>
-        </is>
-      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -21806,11 +19226,6 @@
           <t>https://arpusoft.com/</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr">
-        <is>
-          <t>Area 70 Street 124, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -21846,11 +19261,6 @@
           <t>http://www.tradeaxcorp.com/</t>
         </is>
       </c>
-      <c r="H538" t="inlineStr">
-        <is>
-          <t>Bin Dirham Plaza, 4th Floor, B-Ring Road, Near Grand Hamad Street an</t>
-        </is>
-      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -21886,11 +19296,6 @@
           <t>https://jteservices.com/</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr">
-        <is>
-          <t>3rd Floor- Room:, Gridco Bldg 1 Above American Hospital Hospital, 30</t>
-        </is>
-      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -21926,11 +19331,6 @@
           <t>https://oliviaqatar.com/</t>
         </is>
       </c>
-      <c r="H540" t="inlineStr">
-        <is>
-          <t>Papa John Building 4th Floor Office No# 2, Building No: 146, Street</t>
-        </is>
-      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -21966,11 +19366,6 @@
           <t>http://www.auramanpower.com/</t>
         </is>
       </c>
-      <c r="H541" t="inlineStr">
-        <is>
-          <t>Zone 24 Building number 18 , Floor 2 , Room, 209 Street 840, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -22006,11 +19401,6 @@
           <t>https://alareengroups.com/</t>
         </is>
       </c>
-      <c r="H542" t="inlineStr">
-        <is>
-          <t>ZONE 24, STREET 830, BUILDING, SECOND FLOOR, 4 AL HITEEN STREET, Doh</t>
-        </is>
-      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -22046,11 +19436,6 @@
           <t>http://www.firemasterqa.com/</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr">
-        <is>
-          <t>Zone 24, Bldg 185, Street 220, Floor 2, Office, 104B, B Ring Rd, Doh</t>
-        </is>
-      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -22086,11 +19471,6 @@
           <t>https://www.fresho.qa/</t>
         </is>
       </c>
-      <c r="H544" t="inlineStr">
-        <is>
-          <t>Office 205, Flat 5, Floor 6, Tower 2, Building, Trading Centre, 16 H</t>
-        </is>
-      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -22126,11 +19506,6 @@
           <t>http://www.royalexpresscargo.com/</t>
         </is>
       </c>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>Al matar Centre, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -22166,11 +19541,6 @@
           <t>http://www.peaceentqatar.com/</t>
         </is>
       </c>
-      <c r="H546" t="inlineStr">
-        <is>
-          <t>Barwa Towers, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -22206,11 +19576,6 @@
           <t>https://qatarofficesrent.com/directory/officespace/213-sqm-fitted-office-in-lusail-marina/</t>
         </is>
       </c>
-      <c r="H547" t="inlineStr">
-        <is>
-          <t>Lusail Marina, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -22246,11 +19611,6 @@
           <t>https://siyanafm.com/</t>
         </is>
       </c>
-      <c r="H548" t="inlineStr">
-        <is>
-          <t>7GP4+P4V Marina 50 Tower, 315, Zone 69, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -22286,11 +19646,6 @@
           <t>https://www.ritajwll.com/</t>
         </is>
       </c>
-      <c r="H549" t="inlineStr">
-        <is>
-          <t>The Union Tower, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -22326,11 +19681,6 @@
           <t>http://www.flare.qa/</t>
         </is>
       </c>
-      <c r="H550" t="inlineStr">
-        <is>
-          <t>Manarat Lusail, Floor 25 Lusail Marina, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -22366,11 +19716,6 @@
           <t>https://allayalgroup.com/</t>
         </is>
       </c>
-      <c r="H551" t="inlineStr">
-        <is>
-          <t>:790 building, Area :53 street, Umm Al Dome St</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -22406,11 +19751,6 @@
           <t>http://www.canintlgroup.com/</t>
         </is>
       </c>
-      <c r="H552" t="inlineStr">
-        <is>
-          <t>Can International Management Consultancy, C Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -22446,11 +19786,6 @@
           <t>http://www.skylinedigital.qa/</t>
         </is>
       </c>
-      <c r="H553" t="inlineStr">
-        <is>
-          <t>Office # 2, 5th Floor, Transworld Tower 2, Street # 840, Zone #18 Bu</t>
-        </is>
-      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -22486,11 +19821,6 @@
           <t>https://www.metrogroupqa.com/</t>
         </is>
       </c>
-      <c r="H554" t="inlineStr">
-        <is>
-          <t>Building No. 20, Street 940, Al Khalidiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -22526,11 +19856,6 @@
           <t>http://www.hayyaxpress.com/</t>
         </is>
       </c>
-      <c r="H555" t="inlineStr">
-        <is>
-          <t>Airport St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -22566,11 +19891,6 @@
           <t>http://www.hasratservices.com/</t>
         </is>
       </c>
-      <c r="H556" t="inlineStr">
-        <is>
-          <t>88 Al Aziziya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -22606,11 +19926,6 @@
           <t>https://notezt.com/</t>
         </is>
       </c>
-      <c r="H557" t="inlineStr">
-        <is>
-          <t>Ramada Signal, Zone: 39, Street : 340, Building : 90 (Al Maha Busine</t>
-        </is>
-      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -22646,11 +19961,6 @@
           <t>https://tenworks.qa/</t>
         </is>
       </c>
-      <c r="H558" t="inlineStr">
-        <is>
-          <t>Doha Souq Mall First Floor Al Mirqab Al Jadeed Street, Al Amir St, D</t>
-        </is>
-      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -22686,11 +19996,6 @@
           <t>https://fairdealqatar.com/services/manpower-supplier-in-qatar/</t>
         </is>
       </c>
-      <c r="H559" t="inlineStr">
-        <is>
-          <t>Building No. 48, Street No, 840 Al Matar Al Qadeem St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -22726,11 +20031,6 @@
           <t>https://noor.qa/</t>
         </is>
       </c>
-      <c r="H560" t="inlineStr">
-        <is>
-          <t>No 16, 14th Floor, Al Fardan Office Tower, 61 Al Funduq St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -22766,11 +20066,6 @@
           <t>http://kayroexpressdelivery.com/</t>
         </is>
       </c>
-      <c r="H561" t="inlineStr">
-        <is>
-          <t>Doha City Centre Al Dafna area, Doha, 22744, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -22806,11 +20101,6 @@
           <t>https://www.noblelesse.com/</t>
         </is>
       </c>
-      <c r="H562" t="inlineStr">
-        <is>
-          <t>QFC Tower 1, Fintech Circle, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -22846,11 +20136,6 @@
           <t>https://jecsteam.com/</t>
         </is>
       </c>
-      <c r="H563" t="inlineStr">
-        <is>
-          <t>Al Jazeera Tower, Building, 186 Street 836, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -22886,11 +20171,6 @@
           <t>https://expertgroupqa.com/</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr">
-        <is>
-          <t>Office No. 59, Hub business centre, Mirqab Mall, Al Nasr, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -22926,11 +20206,6 @@
           <t>https://alharibsecurity.com/</t>
         </is>
       </c>
-      <c r="H565" t="inlineStr">
-        <is>
-          <t>Building 355, Ain khalid, Salwa Road Unit14,Zone 56,Street 340, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -22966,11 +20241,6 @@
           <t>https://netmart.qa/</t>
         </is>
       </c>
-      <c r="H566" t="inlineStr">
-        <is>
-          <t>Souq Naif, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -23006,11 +20276,6 @@
           <t>https://sheenincorp.com/contact-us/</t>
         </is>
       </c>
-      <c r="H567" t="inlineStr">
-        <is>
-          <t>Office #10, 2nd Floor, Concord Business Center, Bldg. No, 38, Al Raw</t>
-        </is>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -23046,11 +20311,6 @@
           <t>https://alibtikaria.com/</t>
         </is>
       </c>
-      <c r="H568" t="inlineStr">
-        <is>
-          <t>4th Floor, 92 Office, City Plaza Center, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -23086,11 +20346,6 @@
           <t>https://bazinsolutions.qa/</t>
         </is>
       </c>
-      <c r="H569" t="inlineStr">
-        <is>
-          <t>Grand Hammad St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -23126,11 +20381,6 @@
           <t>http://www.eqatar.com/</t>
         </is>
       </c>
-      <c r="H570" t="inlineStr">
-        <is>
-          <t>Abdulla Bin Thani, NBK building 2nd Floor, P O Box13966, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -23166,11 +20416,6 @@
           <t>http://www.weonegroup.com/</t>
         </is>
       </c>
-      <c r="H571" t="inlineStr">
-        <is>
-          <t>Ar-Rayyan, Furoosiya St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -23206,11 +20451,6 @@
           <t>http://www.premier-lines.com/</t>
         </is>
       </c>
-      <c r="H572" t="inlineStr">
-        <is>
-          <t>Al Meena St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -23246,11 +20486,6 @@
           <t>https://consultiqbusiness.com/</t>
         </is>
       </c>
-      <c r="H573" t="inlineStr">
-        <is>
-          <t>Souq Mall, 2 Office Number - A53, Al sadd, Mirqab al jadeed street ,</t>
-        </is>
-      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -23286,11 +20521,6 @@
           <t>https://www.pccqa.com/</t>
         </is>
       </c>
-      <c r="H574" t="inlineStr">
-        <is>
-          <t>Lusail city Marina, twin Tower A-28 Floor, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -23326,11 +20556,6 @@
           <t>http://www.ahzassociates.co.uk/</t>
         </is>
       </c>
-      <c r="H575" t="inlineStr">
-        <is>
-          <t>M floor, Burj Alfardan tower, 4440 8308, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -23366,11 +20591,6 @@
           <t>https://spine-mena.com/</t>
         </is>
       </c>
-      <c r="H576" t="inlineStr">
-        <is>
-          <t>The Y Tower Commercial, Street 305, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -23406,11 +20626,6 @@
           <t>https://pfts-qatar.com/</t>
         </is>
       </c>
-      <c r="H577" t="inlineStr">
-        <is>
-          <t>Zone 69 Building, City Qatar, 22 Floor Marina 50, 5 Street No.315, L</t>
-        </is>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -23446,11 +20661,6 @@
           <t>https://hiprofilegroup.com/</t>
         </is>
       </c>
-      <c r="H578" t="inlineStr">
-        <is>
-          <t>Zone: 24, Street: 220, Building:185, Floor: 2nd , Office: 207, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -23486,11 +20696,6 @@
           <t>http://www.innovations.qa/</t>
         </is>
       </c>
-      <c r="H579" t="inlineStr">
-        <is>
-          <t>Al Meera Tower, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -23526,11 +20731,6 @@
           <t>http://www.askmahmoudayesh.com/</t>
         </is>
       </c>
-      <c r="H580" t="inlineStr">
-        <is>
-          <t>Al Sadd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -23566,11 +20766,6 @@
           <t>https://nabeenrajsatyaal.com/</t>
         </is>
       </c>
-      <c r="H581" t="inlineStr">
-        <is>
-          <t>Office Number 104 Bin Dirham Plaza, B Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -23606,11 +20801,6 @@
           <t>http://www.haleysgroup.com/</t>
         </is>
       </c>
-      <c r="H582" t="inlineStr">
-        <is>
-          <t>Street No.:، 965 Zone: 56, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -23646,11 +20836,6 @@
           <t>http://www.wrightmenintl.com/</t>
         </is>
       </c>
-      <c r="H583" t="inlineStr">
-        <is>
-          <t>Al Muntazah, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -23686,11 +20871,6 @@
           <t>https://munticonsultancy.com/en</t>
         </is>
       </c>
-      <c r="H584" t="inlineStr">
-        <is>
-          <t>Office No. 125, Floor No. 4, Building, City Plaza, 59 Street 112، Lu</t>
-        </is>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -23726,11 +20906,6 @@
           <t>http://www.salfordeducation.com/</t>
         </is>
       </c>
-      <c r="H585" t="inlineStr">
-        <is>
-          <t>4th Floor 406 Room, Lulu xpress, Bin Dirham Plaza, B Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -23766,11 +20941,6 @@
           <t>http://cignagency.com/</t>
         </is>
       </c>
-      <c r="H586" t="inlineStr">
-        <is>
-          <t>8GFG+9QQ, طريق الريان, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -23806,11 +20976,6 @@
           <t>http://www.brightmindsagency.com/</t>
         </is>
       </c>
-      <c r="H587" t="inlineStr">
-        <is>
-          <t>Floor 25 Lusail Marina, Manarat Lusail, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -23846,11 +21011,6 @@
           <t>https://emigroconsulting.com/</t>
         </is>
       </c>
-      <c r="H588" t="inlineStr">
-        <is>
-          <t>31th floor, office no, Laffan towers, 18 Ambassador st, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -23886,11 +21046,6 @@
           <t>https://mavericks.qa/</t>
         </is>
       </c>
-      <c r="H589" t="inlineStr">
-        <is>
-          <t>Marina Twin Tower A Office 181, Floor 18, 40023979, Lusail</t>
-        </is>
-      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -23926,11 +21081,6 @@
           <t>http://mohhyd.com/</t>
         </is>
       </c>
-      <c r="H590" t="inlineStr">
-        <is>
-          <t>Street 924 Building no 5 Bin Mahmood, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -23966,11 +21116,6 @@
           <t>https://www.worknestconnect.com/</t>
         </is>
       </c>
-      <c r="H591" t="inlineStr">
-        <is>
-          <t>1st floor, Apartment 4 Building No, 33 Street 180، Doha</t>
-        </is>
-      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -24006,11 +21151,6 @@
           <t>https://ivory-consult.com/</t>
         </is>
       </c>
-      <c r="H592" t="inlineStr">
-        <is>
-          <t>Building 114 2nd Floor, Othman Bin Affan St, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -24046,11 +21186,6 @@
           <t>http://www.azmep-int.com/</t>
         </is>
       </c>
-      <c r="H593" t="inlineStr">
-        <is>
-          <t>Building 32 Office 38, 2nd Floor, Zone 56 Street 205, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -24086,11 +21221,6 @@
           <t>http://www.agentsgrp.com/</t>
         </is>
       </c>
-      <c r="H594" t="inlineStr">
-        <is>
-          <t>Newton International School، 1st Floor, Building no - 267, Zone -43,</t>
-        </is>
-      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -24126,11 +21256,6 @@
           <t>http://www.qataraspect.com/</t>
         </is>
       </c>
-      <c r="H595" t="inlineStr">
-        <is>
-          <t>Regus Business Center, D Ring Rd, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -24166,11 +21291,6 @@
           <t>http://al-qaisar.com/</t>
         </is>
       </c>
-      <c r="H596" t="inlineStr">
-        <is>
-          <t>Thakira Road, Alkhor, 60560, 891, Street N, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -24206,11 +21326,6 @@
           <t>https://tcmksa.com/</t>
         </is>
       </c>
-      <c r="H597" t="inlineStr">
-        <is>
-          <t>6CJJ+66R, Al-Rayyan</t>
-        </is>
-      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -24246,11 +21361,6 @@
           <t>https://getglobalgroup.com/qa/</t>
         </is>
       </c>
-      <c r="H598" t="inlineStr">
-        <is>
-          <t>Office No: 10, 1ST Floor, Al Jazeera Business Center, Al Waab Road,</t>
-        </is>
-      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -24286,11 +21396,6 @@
           <t>https://www.hackney.education/</t>
         </is>
       </c>
-      <c r="H599" t="inlineStr">
-        <is>
-          <t>HUB Business, Doha Souq Mall, 2nd Floor, Al Mirqab Al Jadeed St, Doh</t>
-        </is>
-      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -24326,11 +21431,6 @@
           <t>http://consultingwithshan.com/</t>
         </is>
       </c>
-      <c r="H600" t="inlineStr">
-        <is>
-          <t>Level 21, Doha</t>
-        </is>
-      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -24364,11 +21464,6 @@
       <c r="G601" t="inlineStr">
         <is>
           <t>http://www.beamreachconsultancy.com/</t>
-        </is>
-      </c>
-      <c r="H601" t="inlineStr">
-        <is>
-          <t>Office No. 39، Suhaim Bin Hamad Al Saad Barwa Towers, No. 1 Floor No</t>
         </is>
       </c>
     </row>
